--- a/docs/downloads/04/tbl_age_obs_alaotra_ambodivoara.xlsx
+++ b/docs/downloads/04/tbl_age_obs_alaotra_ambodivoara.xlsx
@@ -513,12 +513,6 @@
           <t>71 ans et plus</t>
         </is>
       </c>
-      <c r="C9">
-        <v>4</v>
-      </c>
-      <c r="D9">
-        <v>1.8</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
